--- a/Dev/体魄系统数值一览.xlsx
+++ b/Dev/体魄系统数值一览.xlsx
@@ -14,6 +14,8 @@
     <sheet name="成长-经验获取" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="特质偏移" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="日常衰减" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="热情倍率覆盖" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="器官扩展设计" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +63,11 @@
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="8">
@@ -127,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +183,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2880,4 +2890,603 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>体魄技能 · 热情学习倍率覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>仅对 Physique 技能生效；Prefix 补偿 SkillRecord.Learn 的 xp，先除原版倍率再乘自定义倍率。负经验(衰减)不受影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>热情</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>原版倍率</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>覆盖后倍率</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>无 (None)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>×0.35</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>×1.00</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>无热情也按满速学习，不再打折</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>好奇 (Minor)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>×1.00</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>×1.10</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>略高于原版</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>狂热 (Major)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>×1.50</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>×1.20</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>压缩狂热优势，避免体魄暴涨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>注：原版倍率硬编码为 无 0.35 / 好奇 1.0 / 狂热 1.5（2026-07-30 用户定稿）。实现于 HormonesLogic.cs 的 SkillRecord_Learn_Physique_Patch。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>体魄 → 器官影响 · 扩展设计稿（未实现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>现状：体魄只有 激素伤害减免(1.0→0.5线性) 与 激素恢复(1.0→1.5)，尚无器官层效果。数值顺序 = 虚弱/一般/健康/强壮/卓越</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>设计方向</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>联动原版机制（源码已核实）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>建议数值（虚/一/健/强/卓）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>实现方式</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>平衡性风险与对策</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>器官HP加成
+（器官强韧）</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>BodyPartDef.GetMaxHealth(pawn) 决定部件血量：心15/肺15/肾15/肝20/胃20/脑10。HP归零→MissingBodyPart→功能永久归零</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>-10% / 0 / +5% / +10% / +20%</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>C#：Harmony postfix 补丁 BodyPartDef.GetMaxHealth，仅缩放 depth==Inside 部件</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>心脏15→18后狙心秒杀变难，压缩战斗张力；对策：加成≤+20%，或排除心/脑只强韧内脏</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>★★★ 主推</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>器官效率加成
+（机能强化）</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>PawnCapacityUtility.CalculateTagEfficiency：器官效率=partEfficiency×健康度→驱动五项能力；意识耦合对泵血/呼吸/过滤均有 min(x,1) 限幅</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>-10% / 0 / +2% / +5% / +10%</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>C#：postfix CalculateTagEfficiency，按 pawn 体魄缩放</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>超100%部分主要是损耗缓冲（min(x,1)限幅造不出超人）；与 PhysiqueDisplay 已有 capMods(呼吸等)是两层杠杆，注意别重复给太多</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>致死伤害阈值提升
+（命硬）</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Pawn_HealthTracker.LethalDamageThreshold=150×HealthScale；总伤severity超阈值即死（ShouldBeDead判定链第⑤条）</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>×0.9 / ×1.0 / ×1.05 / ×1.1 / ×1.2</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>C#：patch LethalDamageThreshold getter</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>高体魄「怎么打都不死」；对策：上限+20%，加 Settings 开关</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>出血控制
+（凝血强）</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>BleedRate stat=全局出血率；失血hediff lethalSeverity=1.0 即死；心脏被毁bleedRate=5爆发出血</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>×1.15 / ×1.0 / ×0.95 / ×0.9 / ×0.8</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>纯XML：PhysiqueDisplay hediff stages 加 statFactors→BleedRate</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>低。心脏摧毁的爆发出血仍保留威慑</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>★★★ 零代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>痛觉耐受
+（忍痛）</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>疼痛对意识的绝对扣减最多-0.4；PainShockThreshold stat=痛晕倒地阈值（倒地=保护机制）</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>阈值 ×0.9 / ×1.0 / ×1.05 / ×1.1 / ×1.15</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>纯XML：statFactors→PainShockThreshold</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>痛晕是保护性倒地，阈值过高会战到死都不倒；建议≤+15%</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>★★☆ 零代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>愈合加速
+（恢复快）</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>InjuryHealingFactor stat=伤口自然愈合速度</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>×0.9 / ×1.0 / ×1.1 / ×1.25 / ×1.5</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>纯XML：statFactors→InjuryHealingFactor</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>与现有 GetRecoveryBonus(激素恢复1.0→1.5)是不同系统不冲突；与优质睡眠等恢复手段有叠加</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>★★★ 零代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>免疫增强
+（抗病）</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>ImmunityGainSpeed stat=免疫积累速度；感染 lethalSeverity=1.0 即死</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>×0.9 / ×1.0 / ×1.05 / ×1.1 / ×1.2</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>纯XML：statFactors→ImmunityGainSpeed</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>疾病压迫感下降；虚弱档减益可强化「体弱者易病」叙事</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>★★☆ 零代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>永伤抵抗
+（不易留疤）</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>delicate部件(脑)受伤几乎必转永久疤(permanentInjuryChanceFactor=9999999)；永伤永久降器官健康度→能力</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>永伤概率 ×1.2 / ×1.0 / ×0.85 / ×0.7 / ×0.5</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>C#：patch 永伤转换点（scar生成处）</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>脑永伤是经典长期惩罚，全免失张力；建议卓越仍保留50%概率，或排除脑部</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>内脏命中规避
+（护要害）</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>器官coverage=被击相对权重(心0.02/肺0.025/肾0.017)；BodyPartDef.hitChanceFactors可按伤害类型修正</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>内脏被击权重 ×1.1 / ×1.0 / ×0.95 / ×0.9 / ×0.8</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>C#：patch 命中部位选择链（DamageWorker选part处）</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>与闪避/减伤叠加后高体魄过肉；命中选择链较深，工作量中等</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>器官再生
+（卓越终极）</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>MissingBodyPart ShouldRemove=false永不自愈，只能移植/再生舱；RestorePart可恢复部件</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>卓越限定：每30天随机修复一个缺失/永伤器官</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>C#：HediffComp 定期检测 MissingPart→RestorePart</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>冲击移植经济与仿生体系统；建议超长周期或做成特质/默认关</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>★☆☆ 远期</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>落地建议：D/F/G/E 四项纯 XML 可零代码先做（只改 Hediff_PhysiqueDisplay.xml 的 statFactors），快速验证手感；A/B/C/H/I/J 需 C# patch，按优先级 A→C→B 推进。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>